--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129078368</v>
+        <v>129079253</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,21 +1409,17 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316400</v>
+        <v>316423</v>
       </c>
       <c r="R8" t="n">
-        <v>6565637</v>
+        <v>6565584</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1488,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079253</v>
+        <v>129079461</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1535,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316423</v>
+        <v>316417</v>
       </c>
       <c r="R9" t="n">
-        <v>6565584</v>
+        <v>6565579</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129079461</v>
+        <v>129078368</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,17 +1639,21 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316417</v>
+        <v>316400</v>
       </c>
       <c r="R10" t="n">
-        <v>6565579</v>
+        <v>6565637</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R13" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079767</v>
+        <v>129079570</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R14" t="n">
-        <v>6565616</v>
+        <v>6565587</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129079253</v>
+        <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,17 +1409,21 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316423</v>
+        <v>316400</v>
       </c>
       <c r="R8" t="n">
-        <v>6565584</v>
+        <v>6565637</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079461</v>
+        <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1518,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316417</v>
+        <v>316423</v>
       </c>
       <c r="R9" t="n">
-        <v>6565579</v>
+        <v>6565584</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1599,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129078368</v>
+        <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,21 +1643,17 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316400</v>
+        <v>316417</v>
       </c>
       <c r="R10" t="n">
-        <v>6565637</v>
+        <v>6565579</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079767</v>
+        <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R13" t="n">
-        <v>6565616</v>
+        <v>6565587</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R14" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129078368</v>
+        <v>129079253</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,21 +1409,17 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316400</v>
+        <v>316423</v>
       </c>
       <c r="R8" t="n">
-        <v>6565637</v>
+        <v>6565584</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1488,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079253</v>
+        <v>129079461</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1535,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316423</v>
+        <v>316417</v>
       </c>
       <c r="R9" t="n">
-        <v>6565584</v>
+        <v>6565579</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129079461</v>
+        <v>129078368</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,17 +1639,21 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316417</v>
+        <v>316400</v>
       </c>
       <c r="R10" t="n">
-        <v>6565579</v>
+        <v>6565637</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R13" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079767</v>
+        <v>129079570</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R14" t="n">
-        <v>6565616</v>
+        <v>6565587</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129079253</v>
+        <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,17 +1409,21 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316423</v>
+        <v>316400</v>
       </c>
       <c r="R8" t="n">
-        <v>6565584</v>
+        <v>6565637</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079461</v>
+        <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1518,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316417</v>
+        <v>316423</v>
       </c>
       <c r="R9" t="n">
-        <v>6565579</v>
+        <v>6565584</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1599,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129078368</v>
+        <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,21 +1643,17 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316400</v>
+        <v>316417</v>
       </c>
       <c r="R10" t="n">
-        <v>6565637</v>
+        <v>6565579</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079767</v>
+        <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R13" t="n">
-        <v>6565616</v>
+        <v>6565587</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R14" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2521,6 +2521,128 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129533932</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bittjursdyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>316339</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6565488</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre granskog med mycket död ved/döda träd.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129078368</v>
+        <v>129079253</v>
       </c>
       <c r="B8" t="n">
         <v>98727</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,21 +1409,17 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316400</v>
+        <v>316423</v>
       </c>
       <c r="R8" t="n">
-        <v>6565637</v>
+        <v>6565584</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1488,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079253</v>
+        <v>129079461</v>
       </c>
       <c r="B9" t="n">
         <v>98727</v>
@@ -1518,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1535,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316423</v>
+        <v>316417</v>
       </c>
       <c r="R9" t="n">
-        <v>6565584</v>
+        <v>6565579</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,7 +1599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129079461</v>
+        <v>129078368</v>
       </c>
       <c r="B10" t="n">
         <v>98727</v>
@@ -1643,17 +1639,21 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316417</v>
+        <v>316400</v>
       </c>
       <c r="R10" t="n">
-        <v>6565579</v>
+        <v>6565637</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129079703</v>
+        <v>129079570</v>
       </c>
       <c r="B12" t="n">
         <v>98727</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1883,7 +1883,7 @@
         <v>316411</v>
       </c>
       <c r="R12" t="n">
-        <v>6565626</v>
+        <v>6565587</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B13" t="n">
         <v>98727</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R13" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079767</v>
+        <v>129079703</v>
       </c>
       <c r="B14" t="n">
         <v>98727</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R14" t="n">
-        <v>6565616</v>
+        <v>6565626</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129079426</v>
+        <v>129079009</v>
       </c>
       <c r="B16" t="n">
         <v>98727</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>316422</v>
+        <v>316424</v>
       </c>
       <c r="R16" t="n">
-        <v>6565580</v>
+        <v>6565613</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079009</v>
+        <v>129079426</v>
       </c>
       <c r="B17" t="n">
         <v>98727</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>316424</v>
+        <v>316422</v>
       </c>
       <c r="R17" t="n">
-        <v>6565613</v>
+        <v>6565580</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129079253</v>
+        <v>129078368</v>
       </c>
       <c r="B8" t="n">
         <v>98727</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,17 +1409,21 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316423</v>
+        <v>316400</v>
       </c>
       <c r="R8" t="n">
-        <v>6565584</v>
+        <v>6565637</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1484,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079461</v>
+        <v>129079253</v>
       </c>
       <c r="B9" t="n">
         <v>98727</v>
@@ -1514,7 +1518,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316417</v>
+        <v>316423</v>
       </c>
       <c r="R9" t="n">
-        <v>6565579</v>
+        <v>6565584</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1599,7 +1603,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129078368</v>
+        <v>129079461</v>
       </c>
       <c r="B10" t="n">
         <v>98727</v>
@@ -1639,21 +1643,17 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316400</v>
+        <v>316417</v>
       </c>
       <c r="R10" t="n">
-        <v>6565637</v>
+        <v>6565579</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B12" t="n">
         <v>98727</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R12" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079767</v>
+        <v>129079703</v>
       </c>
       <c r="B13" t="n">
         <v>98727</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R13" t="n">
-        <v>6565616</v>
+        <v>6565626</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079703</v>
+        <v>129079570</v>
       </c>
       <c r="B14" t="n">
         <v>98727</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2113,7 +2113,7 @@
         <v>316411</v>
       </c>
       <c r="R14" t="n">
-        <v>6565626</v>
+        <v>6565587</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129079767</v>
+        <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R12" t="n">
-        <v>6565616</v>
+        <v>6565626</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079703</v>
+        <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1998,7 +1998,7 @@
         <v>316411</v>
       </c>
       <c r="R13" t="n">
-        <v>6565626</v>
+        <v>6565587</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R14" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129079009</v>
+        <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>316424</v>
+        <v>316422</v>
       </c>
       <c r="R16" t="n">
-        <v>6565613</v>
+        <v>6565580</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2408,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079426</v>
+        <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>316422</v>
+        <v>316424</v>
       </c>
       <c r="R17" t="n">
-        <v>6565580</v>
+        <v>6565613</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2526,7 +2526,7 @@
         <v>129533932</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129533932</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079703</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>129079570</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>129079767</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129533932</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -1833,7 +1833,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129079703</v>
+        <v>129079767</v>
       </c>
       <c r="B12" t="n">
         <v>98769</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R12" t="n">
-        <v>6565626</v>
+        <v>6565616</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079570</v>
+        <v>129079175</v>
       </c>
       <c r="B13" t="n">
         <v>98769</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316411</v>
+        <v>316428</v>
       </c>
       <c r="R13" t="n">
-        <v>6565587</v>
+        <v>6565600</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079767</v>
+        <v>129079703</v>
       </c>
       <c r="B14" t="n">
         <v>98769</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R14" t="n">
-        <v>6565616</v>
+        <v>6565626</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129079175</v>
+        <v>129079570</v>
       </c>
       <c r="B15" t="n">
         <v>98769</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>316428</v>
+        <v>316411</v>
       </c>
       <c r="R15" t="n">
-        <v>6565600</v>
+        <v>6565587</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078817</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129079212</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129079527</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129079659</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129078781</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129078706</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>129078368</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129079253</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129079461</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129079110</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129079767</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079175</v>
+        <v>129079703</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316428</v>
+        <v>316411</v>
       </c>
       <c r="R13" t="n">
-        <v>6565600</v>
+        <v>6565626</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079703</v>
+        <v>129079570</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2113,7 +2113,7 @@
         <v>316411</v>
       </c>
       <c r="R14" t="n">
-        <v>6565626</v>
+        <v>6565587</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129079570</v>
+        <v>129079175</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>316411</v>
+        <v>316428</v>
       </c>
       <c r="R15" t="n">
-        <v>6565587</v>
+        <v>6565600</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2296,7 +2296,7 @@
         <v>129079426</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129079009</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -1833,7 +1833,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129079767</v>
+        <v>129079703</v>
       </c>
       <c r="B12" t="n">
         <v>98774</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>316419</v>
+        <v>316411</v>
       </c>
       <c r="R12" t="n">
-        <v>6565616</v>
+        <v>6565626</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079703</v>
+        <v>129079570</v>
       </c>
       <c r="B13" t="n">
         <v>98774</v>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1998,7 +1998,7 @@
         <v>316411</v>
       </c>
       <c r="R13" t="n">
-        <v>6565626</v>
+        <v>6565587</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079570</v>
+        <v>129079767</v>
       </c>
       <c r="B14" t="n">
         <v>98774</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316411</v>
+        <v>316419</v>
       </c>
       <c r="R14" t="n">
-        <v>6565587</v>
+        <v>6565616</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>129533932</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -675,60 +675,68 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129078817</v>
+        <v>129533932</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bittjursdyveln N/O, Dls</t>
+          <t>Bittjursdyveln, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316430</v>
+        <v>316339</v>
       </c>
       <c r="R2" t="n">
-        <v>6565615</v>
+        <v>6565488</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +760,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,13 +774,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
+          <t>Äldre granskog med mycket död ved/döda träd.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129079212</v>
+        <v>129078368</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +827,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,17 +837,21 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316425</v>
+        <v>316400</v>
       </c>
       <c r="R3" t="n">
-        <v>6565591</v>
+        <v>6565637</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129079527</v>
+        <v>129078706</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -945,17 +956,21 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316406</v>
+        <v>316396</v>
       </c>
       <c r="R4" t="n">
-        <v>6565582</v>
+        <v>6565637</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129079659</v>
+        <v>129078781</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1085,7 @@
         <v>316400</v>
       </c>
       <c r="R5" t="n">
-        <v>6565586</v>
+        <v>6565630</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1135,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129078781</v>
+        <v>129078817</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1180,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1182,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>316400</v>
+        <v>316430</v>
       </c>
       <c r="R6" t="n">
-        <v>6565630</v>
+        <v>6565615</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1250,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129078706</v>
+        <v>129079009</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,21 +1305,17 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>316396</v>
+        <v>316424</v>
       </c>
       <c r="R7" t="n">
-        <v>6565637</v>
+        <v>6565613</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1369,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129078368</v>
+        <v>129079110</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,21 +1420,17 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>316400</v>
+        <v>316418</v>
       </c>
       <c r="R8" t="n">
-        <v>6565637</v>
+        <v>6565610</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1488,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129079253</v>
+        <v>129079175</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1525,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1535,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>316423</v>
+        <v>316428</v>
       </c>
       <c r="R9" t="n">
-        <v>6565584</v>
+        <v>6565600</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129079461</v>
+        <v>129079212</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1640,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1650,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>316417</v>
+        <v>316425</v>
       </c>
       <c r="R10" t="n">
-        <v>6565579</v>
+        <v>6565591</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129079110</v>
+        <v>129079253</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1755,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1765,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>316418</v>
+        <v>316423</v>
       </c>
       <c r="R11" t="n">
-        <v>6565610</v>
+        <v>6565584</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1833,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129079703</v>
+        <v>129079426</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1870,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1880,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>316411</v>
+        <v>316422</v>
       </c>
       <c r="R12" t="n">
-        <v>6565626</v>
+        <v>6565580</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1948,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079570</v>
+        <v>129079461</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1995,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>316411</v>
+        <v>316417</v>
       </c>
       <c r="R13" t="n">
-        <v>6565587</v>
+        <v>6565579</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2063,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079767</v>
+        <v>129079527</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2100,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2110,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>316419</v>
+        <v>316406</v>
       </c>
       <c r="R14" t="n">
-        <v>6565616</v>
+        <v>6565582</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2178,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129079175</v>
+        <v>129079570</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2215,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2225,10 +2232,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>316428</v>
+        <v>316411</v>
       </c>
       <c r="R15" t="n">
-        <v>6565600</v>
+        <v>6565587</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2293,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129079426</v>
+        <v>129079659</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2330,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2340,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>316422</v>
+        <v>316400</v>
       </c>
       <c r="R16" t="n">
-        <v>6565580</v>
+        <v>6565586</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2408,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129079009</v>
+        <v>129079703</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,7 +2445,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2455,10 +2462,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>316424</v>
+        <v>316411</v>
       </c>
       <c r="R17" t="n">
-        <v>6565613</v>
+        <v>6565626</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2523,68 +2530,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129533932</v>
+        <v>129079767</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bittjursdyveln, Dls</t>
+          <t>Bittjursdyveln N/O, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>316339</v>
+        <v>316419</v>
       </c>
       <c r="R18" t="n">
-        <v>6565488</v>
+        <v>6565616</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2608,12 +2607,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,12 +2621,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre granskog med mycket död ved/döda träd.</t>
+          <t>Mosseblåbärbarrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 49010-2025 artfynd.xlsx
+++ b/artfynd/A 49010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129533932</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129078368</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129078706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129078781</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129078817</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079009</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1492,6 +1527,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079110</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079175</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1722,6 +1767,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079212</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079253</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1952,6 +2007,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079426</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2067,6 +2127,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079461</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2182,6 +2247,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079527</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079570</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2412,6 +2487,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079659</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2527,6 +2607,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079703</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2642,8 +2727,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129079767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>